--- a/backend/elderlycare-common/src/main/resources/excel_model/CheckOutRegistration.xlsx
+++ b/backend/elderlycare-common/src/main/resources/excel_model/CheckOutRegistration.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -456,7 +456,6 @@
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -485,11 +484,6 @@
           <t>经办人</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>操作</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -517,11 +511,6 @@
           <t>operator</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t>operation</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -547,11 +536,6 @@
           <t>李管家</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>查看详情</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -577,11 +561,6 @@
           <t>王护士</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>查看详情</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -605,11 +584,6 @@
       <c r="E5" s="2" t="inlineStr">
         <is>
           <t>李管家</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>查看详情</t>
         </is>
       </c>
     </row>
